--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/publication/FigD5_7_D4_D5_complementarity_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/publication/FigD5_7_D4_D5_complementarity_source_data.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,21 @@
           <t>analysis_unit</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_run_id</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_calibration_id</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_sha256</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -484,16 +499,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1447844203117691</v>
+        <v>0.1188315838545302</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05864101364003914</v>
+        <v>0.04710521315174847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2481575241197819</v>
+        <v>0.1995383959868399</v>
       </c>
       <c r="F2" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G2" t="n">
         <v>23</v>
@@ -503,6 +518,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,12 +546,12 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09865786831358302</v>
+        <v>0.08087269655817959</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G3" t="n">
         <v>23</v>
@@ -531,6 +561,21 @@
           <t>pair_hour_descriptive</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,12 +589,12 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1358844307968348</v>
+        <v>0.1084581198320218</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G4" t="n">
         <v>23</v>
@@ -559,6 +604,21 @@
           <t>rank_residual_pair_month_regime_adjusted</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -572,16 +632,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2353553220268443</v>
+        <v>0.2293999425782371</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1659160096373187</v>
+        <v>0.166535972040293</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3067607568531292</v>
+        <v>0.2930904213393423</v>
       </c>
       <c r="F5" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G5" t="n">
         <v>23</v>
@@ -591,6 +651,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,12 +679,12 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.216176000730294</v>
+        <v>1.187442266664128</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G6" t="n">
         <v>23</v>
@@ -619,6 +694,21 @@
           <t>pair_hour_descriptive</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -632,16 +722,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1384181377374037</v>
+        <v>0.1709287648135908</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05529201011971745</v>
+        <v>0.08872559112986397</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2234997467361922</v>
+        <v>0.243624764309084</v>
       </c>
       <c r="F7" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G7" t="n">
         <v>37</v>
@@ -651,6 +741,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -664,12 +769,12 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.09339694266341063</v>
+        <v>0.1147791249723404</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G8" t="n">
         <v>37</v>
@@ -679,6 +784,21 @@
           <t>pair_hour_descriptive</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -692,12 +812,12 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1401100141131972</v>
+        <v>0.1427654099274315</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G9" t="n">
         <v>37</v>
@@ -707,6 +827,21 @@
           <t>rank_residual_pair_month_regime_adjusted</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -720,16 +855,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3131121120707467</v>
+        <v>0.3403883282940512</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2537102351377589</v>
+        <v>0.2752831403224458</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3677112566087144</v>
+        <v>0.3989756986314746</v>
       </c>
       <c r="F10" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G10" t="n">
         <v>37</v>
@@ -739,6 +874,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -752,12 +902,12 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.142665707072681</v>
+        <v>1.173796699884706</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G11" t="n">
         <v>37</v>
@@ -765,6 +915,21 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>pair_hour_descriptive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -779,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,12 +995,37 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>descriptive_estimable</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>status_reason</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>analysis_unit</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_run_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_calibration_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_sha256</t>
         </is>
       </c>
     </row>
@@ -856,16 +1046,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1648871709266774</v>
+        <v>0.1598127213982356</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02447081947965471</v>
+        <v>0.02044745877641351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3135450742565269</v>
+        <v>0.3032622893615987</v>
       </c>
       <c r="G2" t="n">
-        <v>11228</v>
+        <v>11299</v>
       </c>
       <c r="H2" t="n">
         <v>23</v>
@@ -873,14 +1063,35 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -901,16 +1112,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1263995445036044</v>
+        <v>0.0797093057588512</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01360351484083131</v>
+        <v>-0.05114047511035813</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2615421231913523</v>
+        <v>0.2075996729811067</v>
       </c>
       <c r="G3" t="n">
-        <v>7148</v>
+        <v>8475</v>
       </c>
       <c r="H3" t="n">
         <v>23</v>
@@ -918,14 +1129,35 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -946,16 +1178,12 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.513228826754611</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2362053926147847</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5173160799243584</v>
-      </c>
+        <v>0.4402850199851668</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>1043</v>
+        <v>1120</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -963,14 +1191,35 @@
       <c r="I4" t="b">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -991,16 +1240,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1657400678939403</v>
+        <v>0.08823341372881678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03363776161359748</v>
+        <v>-0.009280771995007807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.300562193074388</v>
+        <v>0.1764686539828898</v>
       </c>
       <c r="G5" t="n">
-        <v>6507</v>
+        <v>7168</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
@@ -1008,14 +1257,35 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1036,16 +1306,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1742452418183653</v>
+        <v>0.1954746506358939</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09241199048872731</v>
+        <v>0.1077290142656085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2866986480689279</v>
+        <v>0.3203813378595837</v>
       </c>
       <c r="G6" t="n">
-        <v>6129</v>
+        <v>6460</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -1053,14 +1323,35 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1081,16 +1372,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05414477311593065</v>
+        <v>0.04621402964994677</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03133808772954599</v>
+        <v>-0.04907784215363829</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1709850332616494</v>
+        <v>0.1687900228078297</v>
       </c>
       <c r="G7" t="n">
-        <v>4697</v>
+        <v>5026</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -1098,14 +1389,35 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1126,16 +1438,12 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.184785963710277</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.06695340398379235</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3290210775254468</v>
-      </c>
+        <v>0.2007104479213656</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>4452</v>
+        <v>4668</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -1143,14 +1451,35 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1171,16 +1500,12 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06642735137048236</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.02624940553157378</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.212114224817723</v>
-      </c>
+        <v>0.05948948626695483</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>3885</v>
+        <v>4193</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
@@ -1188,14 +1513,35 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1216,16 +1562,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1555001530883052</v>
+        <v>0.1500191582519086</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04641194495913831</v>
+        <v>0.03850358759327382</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2345068760554251</v>
+        <v>0.2267186973945168</v>
       </c>
       <c r="G10" t="n">
-        <v>3907</v>
+        <v>4123</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
@@ -1233,14 +1579,35 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1261,16 +1628,12 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1406568563778936</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.05774629775781958</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.2618012704749982</v>
-      </c>
+        <v>0.1607173768372455</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>2367</v>
+        <v>2513</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -1278,14 +1641,35 @@
       <c r="I11" t="b">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1306,16 +1690,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3650041288334026</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.09715700249340195</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.5851337578385559</v>
-      </c>
+        <v>0.1996183204300839</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>3636</v>
+        <v>4137</v>
       </c>
       <c r="H12" t="n">
         <v>5</v>
@@ -1323,14 +1703,35 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1351,16 +1752,12 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.008782579931353524</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.05787180256159399</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.2362053926147847</v>
-      </c>
+        <v>-0.03715756645859602</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -1368,14 +1765,35 @@
       <c r="I13" t="b">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1396,16 +1814,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.254709523139854</v>
+        <v>0.24716166757365</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04264086851853467</v>
+        <v>0.02349297625726329</v>
       </c>
       <c r="F14" t="n">
-        <v>0.444162069228968</v>
+        <v>0.4411344102177019</v>
       </c>
       <c r="G14" t="n">
-        <v>2753</v>
+        <v>2824</v>
       </c>
       <c r="H14" t="n">
         <v>23</v>
@@ -1413,14 +1831,35 @@
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1441,13 +1880,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1373139295349436</v>
+        <v>0.128732791895169</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08199013374604791</v>
+        <v>-0.09739145461226639</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3603516325522506</v>
+        <v>0.3397264958015012</v>
       </c>
       <c r="G15" t="n">
         <v>2825</v>
@@ -1458,14 +1897,35 @@
       <c r="I15" t="b">
         <v>1</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1486,13 +1946,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1447694868045275</v>
+        <v>-0.1447789726746014</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3750686239476251</v>
+        <v>-0.3684639307392786</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0978059168099614</v>
+        <v>0.0987949365805483</v>
       </c>
       <c r="G16" t="n">
         <v>2825</v>
@@ -1503,14 +1963,35 @@
       <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1531,13 +2012,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2586612710188049</v>
+        <v>0.2548884117033289</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04426007925094853</v>
+        <v>0.02977644760351317</v>
       </c>
       <c r="F17" t="n">
-        <v>0.468260764427261</v>
+        <v>0.458571308054424</v>
       </c>
       <c r="G17" t="n">
         <v>2825</v>
@@ -1548,14 +2029,35 @@
       <c r="I17" t="b">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1576,16 +2078,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1181849870419339</v>
+        <v>0.1174065870459576</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1092960312193946</v>
+        <v>-0.1057320290409087</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3431882707025672</v>
+        <v>0.3408855475779765</v>
       </c>
       <c r="G18" t="n">
-        <v>2593</v>
+        <v>2825</v>
       </c>
       <c r="H18" t="n">
         <v>23</v>
@@ -1593,14 +2095,35 @@
       <c r="I18" t="b">
         <v>1</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1621,16 +2144,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.2728216217044547</v>
+        <v>0.2326659017374983</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04513496143531474</v>
+        <v>0.01782860933143079</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4875977109211334</v>
+        <v>0.450705114853767</v>
       </c>
       <c r="G19" t="n">
-        <v>2417</v>
+        <v>2825</v>
       </c>
       <c r="H19" t="n">
         <v>23</v>
@@ -1638,14 +2161,35 @@
       <c r="I19" t="b">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1666,16 +2210,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.09219003131807918</v>
+        <v>-0.1389312561316479</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2639428801196977</v>
+        <v>-0.305483084219249</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09110239417663873</v>
+        <v>0.05240985521479488</v>
       </c>
       <c r="G20" t="n">
-        <v>2138</v>
+        <v>2825</v>
       </c>
       <c r="H20" t="n">
         <v>23</v>
@@ -1683,14 +2227,35 @@
       <c r="I20" t="b">
         <v>1</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1711,16 +2276,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1073101155509427</v>
+        <v>0.08850978279548977</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.001791366959307334</v>
+        <v>-0.02240861765470454</v>
       </c>
       <c r="F21" t="n">
-        <v>0.225659239983356</v>
+        <v>0.2031283389567795</v>
       </c>
       <c r="G21" t="n">
-        <v>24103</v>
+        <v>24179</v>
       </c>
       <c r="H21" t="n">
         <v>37</v>
@@ -1728,14 +2293,35 @@
       <c r="I21" t="b">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1756,16 +2342,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1841892521803911</v>
+        <v>0.249933899818186</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07742004420279165</v>
+        <v>0.1396113269718088</v>
       </c>
       <c r="F22" t="n">
-        <v>0.281744865245054</v>
+        <v>0.3432159250277849</v>
       </c>
       <c r="G22" t="n">
-        <v>13884</v>
+        <v>18192</v>
       </c>
       <c r="H22" t="n">
         <v>37</v>
@@ -1773,14 +2359,35 @@
       <c r="I22" t="b">
         <v>1</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1801,16 +2408,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1826717421780263</v>
+        <v>0.2608244375254192</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06406448377681202</v>
+        <v>0.135978299732926</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3061443918434869</v>
+        <v>0.3752903022006445</v>
       </c>
       <c r="G23" t="n">
-        <v>15834</v>
+        <v>18614</v>
       </c>
       <c r="H23" t="n">
         <v>17</v>
@@ -1818,14 +2425,35 @@
       <c r="I23" t="b">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1846,16 +2474,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.145565227789108</v>
+        <v>0.09819348253400323</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01399852844895695</v>
+        <v>-0.01108541438983866</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2746806958357535</v>
+        <v>0.1970378857516808</v>
       </c>
       <c r="G24" t="n">
-        <v>9390</v>
+        <v>10220</v>
       </c>
       <c r="H24" t="n">
         <v>13</v>
@@ -1863,14 +2491,35 @@
       <c r="I24" t="b">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1891,16 +2540,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1685180916765592</v>
+        <v>0.1910526677041139</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07949895761956288</v>
+        <v>0.09996746995845496</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2776680993908811</v>
+        <v>0.3094360034803626</v>
       </c>
       <c r="G25" t="n">
-        <v>6562</v>
+        <v>6929</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
@@ -1908,14 +2557,35 @@
       <c r="I25" t="b">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1936,16 +2606,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.05685486108107315</v>
+        <v>0.04779975957437405</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.03986906834314594</v>
+        <v>-0.05995896924131323</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1654020941276133</v>
+        <v>0.1574734162258497</v>
       </c>
       <c r="G26" t="n">
-        <v>6189</v>
+        <v>6594</v>
       </c>
       <c r="H26" t="n">
         <v>7</v>
@@ -1953,14 +2623,35 @@
       <c r="I26" t="b">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2675,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -1992,14 +2683,35 @@
       <c r="I27" t="b">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>insufficient_hours_blocks_or_score_variation</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2020,16 +2732,12 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1746301128847442</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.06026774555830292</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.3143020574276115</v>
-      </c>
+        <v>0.1917876472307921</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>4807</v>
+        <v>5046</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -2037,14 +2745,35 @@
       <c r="I28" t="b">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2065,16 +2794,12 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.04839302066996519</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.04202609377788903</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.1848183698633858</v>
-      </c>
+        <v>0.04172147146409691</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>4509</v>
+        <v>4879</v>
       </c>
       <c r="H29" t="n">
         <v>5</v>
@@ -2082,14 +2807,35 @@
       <c r="I29" t="b">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2110,16 +2856,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1569161339565935</v>
+        <v>0.1497605480172237</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05096788767684764</v>
+        <v>0.03986727305263311</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2206561010077184</v>
+        <v>0.2146163969261723</v>
       </c>
       <c r="G30" t="n">
-        <v>4960</v>
+        <v>5208</v>
       </c>
       <c r="H30" t="n">
         <v>6</v>
@@ -2127,14 +2873,35 @@
       <c r="I30" t="b">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2155,16 +2922,12 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1053591576112445</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0.06974551297344025</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.2266223765069477</v>
-      </c>
+        <v>0.1237122592055719</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>4782</v>
+        <v>5040</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -2172,14 +2935,35 @@
       <c r="I31" t="b">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2200,16 +2984,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.4629525145587797</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.09329345966796689</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.6355960240523886</v>
-      </c>
+        <v>0.3257640751239155</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>4612</v>
+        <v>5208</v>
       </c>
       <c r="H32" t="n">
         <v>5</v>
@@ -2217,14 +2997,35 @@
       <c r="I32" t="b">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2245,16 +3046,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.05869916163315617</v>
+        <v>0.07138776183439244</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2017337571775558</v>
+        <v>-0.205172509800874</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3415260208407785</v>
+        <v>0.3873738525301996</v>
       </c>
       <c r="G33" t="n">
-        <v>4628</v>
+        <v>4998</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
@@ -2262,14 +3063,35 @@
       <c r="I33" t="b">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2290,16 +3112,12 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.09606238141869745</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.03264083321930808</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.2151694544439619</v>
-      </c>
+        <v>0.1257937734771043</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>3713</v>
+        <v>4704</v>
       </c>
       <c r="H34" t="n">
         <v>5</v>
@@ -2307,14 +3125,35 @@
       <c r="I34" t="b">
         <v>1</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2335,16 +3174,12 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.3383504951945573</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.2098416178167383</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.4768416850383361</v>
-      </c>
+        <v>0.3919183763708834</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>4005</v>
+        <v>5132</v>
       </c>
       <c r="H35" t="n">
         <v>5</v>
@@ -2352,14 +3187,35 @@
       <c r="I35" t="b">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2380,16 +3236,12 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.04354408963858887</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.467758799771775</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.4141241955859272</v>
-      </c>
+        <v>0.002616591107560273</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>1971</v>
+        <v>2156</v>
       </c>
       <c r="H36" t="n">
         <v>3</v>
@@ -2397,14 +3249,35 @@
       <c r="I36" t="b">
         <v>1</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2425,16 +3298,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.1661977852485299</v>
+        <v>0.153386101794495</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.03295308865950863</v>
+        <v>-0.05747535146914793</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3589342604749517</v>
+        <v>0.3397674720916619</v>
       </c>
       <c r="G37" t="n">
-        <v>5969</v>
+        <v>6044</v>
       </c>
       <c r="H37" t="n">
         <v>37</v>
@@ -2442,14 +3315,35 @@
       <c r="I37" t="b">
         <v>1</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2470,16 +3364,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.03007163084027335</v>
+        <v>0.01481212208169198</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.1943356407000376</v>
+        <v>-0.1964467217113791</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2494087771034263</v>
+        <v>0.2379039090324816</v>
       </c>
       <c r="G38" t="n">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="H38" t="n">
         <v>37</v>
@@ -2487,14 +3381,35 @@
       <c r="I38" t="b">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2515,13 +3430,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1676713913448296</v>
+        <v>0.1460952880188521</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.02551803006772493</v>
+        <v>-0.06255067730168695</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3459133528337808</v>
+        <v>0.3106787301503341</v>
       </c>
       <c r="G39" t="n">
         <v>6045</v>
@@ -2532,14 +3447,35 @@
       <c r="I39" t="b">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2560,13 +3496,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0470028544447773</v>
+        <v>0.02275386446749715</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.1281995582378314</v>
+        <v>-0.1492998099358729</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2249743563397756</v>
+        <v>0.2215409657159585</v>
       </c>
       <c r="G40" t="n">
         <v>6045</v>
@@ -2577,14 +3513,35 @@
       <c r="I40" t="b">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2605,16 +3562,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1823509955763661</v>
+        <v>0.1805133147913669</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.001652947574804879</v>
+        <v>-0.007679192376166156</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3620129403030196</v>
+        <v>0.3571454981283404</v>
       </c>
       <c r="G41" t="n">
-        <v>5650</v>
+        <v>6064</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -2622,14 +3579,35 @@
       <c r="I41" t="b">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2650,16 +3628,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.5081551132491087</v>
+        <v>0.5369511811396844</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3421980427888295</v>
+        <v>0.3900795351799278</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6191530351249586</v>
+        <v>0.6241342020362962</v>
       </c>
       <c r="G42" t="n">
-        <v>4303</v>
+        <v>6064</v>
       </c>
       <c r="H42" t="n">
         <v>37</v>
@@ -2667,14 +3645,35 @@
       <c r="I42" t="b">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2695,16 +3694,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-0.100472819525351</v>
+        <v>0.004864951203155672</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2624264766546522</v>
+        <v>-0.173404562961704</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05907050036774079</v>
+        <v>0.1753492915771968</v>
       </c>
       <c r="G43" t="n">
-        <v>3931</v>
+        <v>6064</v>
       </c>
       <c r="H43" t="n">
         <v>37</v>
@@ -2712,14 +3711,35 @@
       <c r="I43" t="b">
         <v>1</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>synchronized_7d_time_block</t>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -2734,7 +3754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2768,6 +3788,21 @@
           <t>production_weights_changed</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_run_id</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_calibration_id</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_sha256</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2790,6 +3825,21 @@
       <c r="F2" t="b">
         <v>0</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2811,6 +3861,21 @@
       </c>
       <c r="F3" t="b">
         <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
       </c>
     </row>
   </sheetData>
